--- a/grupos/2ALCM - Estadisticos 20232.xlsx
+++ b/grupos/2ALCM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="141">
   <si>
     <t>Materia</t>
   </si>
@@ -221,21 +221,21 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Sanchez Morales Gilberto</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>Sanchez Morales Gilberto</t>
-  </si>
-  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
@@ -254,97 +254,76 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BONOLA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>SANTOS</t>
   </si>
   <si>
+    <t>ALTAMIRA</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>ESCOBEDO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>PASTRANA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>ALTAMIRA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ESCOBEDO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>MIXTECO</t>
+    <t>ARIAS</t>
   </si>
   <si>
     <t>VARILLAS</t>
@@ -383,9 +362,6 @@
     <t>BERISTAIN</t>
   </si>
   <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
     <t>TEZOCO</t>
   </si>
   <si>
@@ -395,24 +371,15 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ANGEL NAIN</t>
-  </si>
-  <si>
-    <t>ANIELA SAMANTA</t>
+    <t>ALEX TADEO</t>
+  </si>
+  <si>
+    <t>ARELI DANAE</t>
   </si>
   <si>
     <t>MIRANDA</t>
   </si>
   <si>
-    <t>MARGARITA</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>GUADALUPE ANAHI</t>
-  </si>
-  <si>
     <t>LINET</t>
   </si>
   <si>
@@ -462,9 +429,6 @@
   </si>
   <si>
     <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MELANY</t>
   </si>
   <si>
     <t>CONCEPCION GUADALUPE</t>
@@ -1041,31 +1005,31 @@
         <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -1095,31 +1059,31 @@
         <v>-1</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF4">
         <v>9</v>
       </c>
       <c r="AG4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH4">
         <v>6</v>
       </c>
       <c r="AI4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ4">
         <v>-1</v>
       </c>
       <c r="AK4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1154,31 +1118,31 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -1208,13 +1172,13 @@
         <v>-1</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF5">
         <v>10</v>
@@ -1223,10 +1187,10 @@
         <v>10</v>
       </c>
       <c r="AH5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ5">
         <v>-1</v>
@@ -1267,31 +1231,31 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1321,7 +1285,7 @@
         <v>-1</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD6">
         <v>5</v>
@@ -1333,10 +1297,10 @@
         <v>6</v>
       </c>
       <c r="AG6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI6">
         <v>5</v>
@@ -1345,7 +1309,7 @@
         <v>-1</v>
       </c>
       <c r="AK6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1380,31 +1344,31 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1440,13 +1404,13 @@
         <v>6</v>
       </c>
       <c r="AE7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF7">
         <v>6</v>
       </c>
       <c r="AG7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH7">
         <v>6</v>
@@ -1458,7 +1422,7 @@
         <v>-1</v>
       </c>
       <c r="AK7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1493,31 +1457,31 @@
         <v>4</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1547,19 +1511,19 @@
         <v>-1</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF8">
         <v>6</v>
       </c>
       <c r="AG8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH8">
         <v>5</v>
@@ -1606,31 +1570,31 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1660,10 +1624,10 @@
         <v>-1</v>
       </c>
       <c r="AC9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AD9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE9">
         <v>8</v>
@@ -1675,10 +1639,10 @@
         <v>9</v>
       </c>
       <c r="AH9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ9">
         <v>-1</v>
@@ -1719,31 +1683,31 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1773,7 +1737,7 @@
         <v>-1</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD10">
         <v>6</v>
@@ -1785,10 +1749,10 @@
         <v>7</v>
       </c>
       <c r="AG10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI10">
         <v>7</v>
@@ -1797,7 +1761,7 @@
         <v>-1</v>
       </c>
       <c r="AK10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1832,31 +1796,31 @@
         <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1889,7 +1853,7 @@
         <v>9</v>
       </c>
       <c r="AD11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE11">
         <v>9</v>
@@ -1898,13 +1862,13 @@
         <v>9</v>
       </c>
       <c r="AG11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ11">
         <v>-1</v>
@@ -1945,31 +1909,31 @@
         <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -2058,31 +2022,31 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -2118,16 +2082,16 @@
         <v>9</v>
       </c>
       <c r="AE13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF13">
         <v>9</v>
       </c>
       <c r="AG13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI13">
         <v>9</v>
@@ -2136,7 +2100,7 @@
         <v>-1</v>
       </c>
       <c r="AK13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2171,31 +2135,31 @@
         <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -2225,22 +2189,22 @@
         <v>-1</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD14">
         <v>6</v>
       </c>
       <c r="AE14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF14">
         <v>7</v>
       </c>
       <c r="AG14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI14">
         <v>6</v>
@@ -2284,31 +2248,31 @@
         <v>4</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -2397,31 +2361,31 @@
         <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -2451,10 +2415,10 @@
         <v>-1</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE16">
         <v>9</v>
@@ -2469,7 +2433,7 @@
         <v>10</v>
       </c>
       <c r="AI16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ16">
         <v>-1</v>
@@ -2510,31 +2474,31 @@
         <v>4</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2570,7 +2534,7 @@
         <v>5</v>
       </c>
       <c r="AE17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF17">
         <v>5</v>
@@ -2623,31 +2587,31 @@
         <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2736,31 +2700,31 @@
         <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2790,7 +2754,7 @@
         <v>-1</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD19">
         <v>6</v>
@@ -2802,19 +2766,19 @@
         <v>7</v>
       </c>
       <c r="AG19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH19">
         <v>8</v>
       </c>
       <c r="AI19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ19">
         <v>-1</v>
       </c>
       <c r="AK19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2849,31 +2813,31 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2903,13 +2867,13 @@
         <v>-1</v>
       </c>
       <c r="AC20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD20">
         <v>5</v>
       </c>
       <c r="AE20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF20">
         <v>6</v>
@@ -2918,7 +2882,7 @@
         <v>8</v>
       </c>
       <c r="AH20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI20">
         <v>6</v>
@@ -2927,7 +2891,7 @@
         <v>-1</v>
       </c>
       <c r="AK20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -2962,31 +2926,31 @@
         <v>4</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -3075,31 +3039,31 @@
         <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -3132,7 +3096,7 @@
         <v>8</v>
       </c>
       <c r="AD22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE22">
         <v>9</v>
@@ -3141,19 +3105,19 @@
         <v>8</v>
       </c>
       <c r="AG22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ22">
         <v>-1</v>
       </c>
       <c r="AK22">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -3188,31 +3152,31 @@
         <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -3257,7 +3221,7 @@
         <v>8</v>
       </c>
       <c r="AH23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI23">
         <v>5</v>
@@ -3266,7 +3230,7 @@
         <v>-1</v>
       </c>
       <c r="AK23">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -3301,31 +3265,31 @@
         <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -3355,10 +3319,10 @@
         <v>-1</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE24">
         <v>7</v>
@@ -3370,16 +3334,16 @@
         <v>8</v>
       </c>
       <c r="AH24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ24">
         <v>-1</v>
       </c>
       <c r="AK24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -3414,31 +3378,31 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -3468,13 +3432,13 @@
         <v>-1</v>
       </c>
       <c r="AC25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF25">
         <v>8</v>
@@ -3483,7 +3447,7 @@
         <v>9</v>
       </c>
       <c r="AH25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI25">
         <v>7</v>
@@ -3492,7 +3456,7 @@
         <v>-1</v>
       </c>
       <c r="AK25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -3527,31 +3491,31 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -3584,7 +3548,7 @@
         <v>9</v>
       </c>
       <c r="AD26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE26">
         <v>8</v>
@@ -3593,13 +3557,13 @@
         <v>8</v>
       </c>
       <c r="AG26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ26">
         <v>-1</v>
@@ -3640,31 +3604,31 @@
         <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T27">
         <v>-1</v>
@@ -3694,7 +3658,7 @@
         <v>-1</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD27">
         <v>7</v>
@@ -3706,13 +3670,13 @@
         <v>7</v>
       </c>
       <c r="AG27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ27">
         <v>-1</v>
@@ -3753,31 +3717,31 @@
         <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
         <v>-1</v>
@@ -3807,7 +3771,7 @@
         <v>-1</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD28">
         <v>6</v>
@@ -3819,10 +3783,10 @@
         <v>6</v>
       </c>
       <c r="AG28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI28">
         <v>7</v>
@@ -3866,31 +3830,31 @@
         <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>-1</v>
@@ -3923,7 +3887,7 @@
         <v>9</v>
       </c>
       <c r="AD29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE29">
         <v>9</v>
@@ -3932,19 +3896,19 @@
         <v>9</v>
       </c>
       <c r="AG29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ29">
         <v>-1</v>
       </c>
       <c r="AK29">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:37">
@@ -3979,31 +3943,31 @@
         <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>-1</v>
@@ -4033,31 +3997,31 @@
         <v>-1</v>
       </c>
       <c r="AC30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF30">
         <v>7</v>
       </c>
       <c r="AG30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH30">
         <v>5</v>
       </c>
       <c r="AI30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ30">
         <v>-1</v>
       </c>
       <c r="AK30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -4092,31 +4056,31 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>-1</v>
@@ -4149,7 +4113,7 @@
         <v>8</v>
       </c>
       <c r="AD31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE31">
         <v>9</v>
@@ -4161,10 +4125,10 @@
         <v>10</v>
       </c>
       <c r="AH31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ31">
         <v>-1</v>
@@ -4205,31 +4169,31 @@
         <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T32">
         <v>-1</v>
@@ -4259,7 +4223,7 @@
         <v>-1</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AD32">
         <v>6</v>
@@ -4271,19 +4235,19 @@
         <v>6</v>
       </c>
       <c r="AG32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ32">
         <v>-1</v>
       </c>
       <c r="AK32">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:37">
@@ -4318,31 +4282,31 @@
         <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
         <v>-1</v>
@@ -4372,13 +4336,13 @@
         <v>-1</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AD33">
         <v>5</v>
       </c>
       <c r="AE33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF33">
         <v>6</v>
@@ -4396,7 +4360,7 @@
         <v>-1</v>
       </c>
       <c r="AK33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:37">
@@ -4431,31 +4395,31 @@
         <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>-1</v>
@@ -4488,10 +4452,10 @@
         <v>10</v>
       </c>
       <c r="AD34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF34">
         <v>10</v>
@@ -4544,31 +4508,31 @@
         <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T35">
         <v>-1</v>
@@ -4604,7 +4568,7 @@
         <v>5</v>
       </c>
       <c r="AE35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF35">
         <v>6</v>
@@ -4613,7 +4577,7 @@
         <v>9</v>
       </c>
       <c r="AH35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI35">
         <v>6</v>
@@ -4622,7 +4586,7 @@
         <v>-1</v>
       </c>
       <c r="AK35">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:37">
@@ -4657,31 +4621,31 @@
         <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
         <v>-1</v>
@@ -4714,7 +4678,7 @@
         <v>10</v>
       </c>
       <c r="AD36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE36">
         <v>10</v>
@@ -4770,31 +4734,31 @@
         <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N37">
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T37">
         <v>-1</v>
@@ -4824,7 +4788,7 @@
         <v>-1</v>
       </c>
       <c r="AC37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD37">
         <v>7</v>
@@ -4839,7 +4803,7 @@
         <v>10</v>
       </c>
       <c r="AH37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI37">
         <v>6</v>
@@ -4883,31 +4847,31 @@
         <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N38">
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
         <v>-1</v>
@@ -4940,7 +4904,7 @@
         <v>9</v>
       </c>
       <c r="AD38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE38">
         <v>8</v>
@@ -4949,7 +4913,7 @@
         <v>9</v>
       </c>
       <c r="AG38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH38">
         <v>7</v>
@@ -4996,31 +4960,31 @@
         <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N39">
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T39">
         <v>-1</v>
@@ -5050,7 +5014,7 @@
         <v>-1</v>
       </c>
       <c r="AC39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD39">
         <v>6</v>
@@ -5062,10 +5026,10 @@
         <v>8</v>
       </c>
       <c r="AG39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI39">
         <v>6</v>
@@ -5074,7 +5038,7 @@
         <v>-1</v>
       </c>
       <c r="AK39">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:37">
@@ -5109,31 +5073,31 @@
         <v>6</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N40">
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T40">
         <v>-1</v>
@@ -5169,16 +5133,16 @@
         <v>5</v>
       </c>
       <c r="AE40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF40">
         <v>6</v>
       </c>
       <c r="AG40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI40">
         <v>5</v>
@@ -5187,7 +5151,7 @@
         <v>-1</v>
       </c>
       <c r="AK40">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:37">
@@ -5222,31 +5186,31 @@
         <v>7</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N41">
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T41">
         <v>-1</v>
@@ -5276,7 +5240,7 @@
         <v>-1</v>
       </c>
       <c r="AC41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD41">
         <v>10</v>
@@ -5288,19 +5252,19 @@
         <v>8</v>
       </c>
       <c r="AG41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ41">
         <v>-1</v>
       </c>
       <c r="AK41">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:37">
@@ -5335,31 +5299,31 @@
         <v>7</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N42">
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T42">
         <v>-1</v>
@@ -5389,7 +5353,7 @@
         <v>-1</v>
       </c>
       <c r="AC42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD42">
         <v>5</v>
@@ -5401,19 +5365,19 @@
         <v>6</v>
       </c>
       <c r="AG42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ42">
         <v>-1</v>
       </c>
       <c r="AK42">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5594,7 +5558,7 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -5606,7 +5570,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -5621,7 +5585,7 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -5633,7 +5597,7 @@
         <v>100</v>
       </c>
       <c r="X4">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y4">
         <v>100</v>
@@ -5680,7 +5644,7 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -5707,7 +5671,7 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="U5">
         <v>100</v>
@@ -5766,7 +5730,7 @@
         <v>96.7</v>
       </c>
       <c r="K6">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -5778,22 +5742,22 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P6">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R6">
         <v>100</v>
       </c>
       <c r="S6">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="T6">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -5805,19 +5769,19 @@
         <v>100</v>
       </c>
       <c r="X6">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y6">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="Z6">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AA6">
         <v>100</v>
       </c>
       <c r="AB6">
-        <v>96.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:28">
@@ -5852,7 +5816,7 @@
         <v>91.7</v>
       </c>
       <c r="K7">
-        <v>52.9</v>
+        <v>69.2</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -5864,22 +5828,22 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q7">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R7">
         <v>100</v>
       </c>
       <c r="S7">
-        <v>91.7</v>
+        <v>94.2</v>
       </c>
       <c r="T7">
-        <v>52.9</v>
+        <v>69.2</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -5891,19 +5855,19 @@
         <v>100</v>
       </c>
       <c r="X7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y7">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Z7">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AA7">
         <v>100</v>
       </c>
       <c r="AB7">
-        <v>91.7</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="8" spans="1:28">
@@ -5938,7 +5902,7 @@
         <v>96.7</v>
       </c>
       <c r="K8">
-        <v>52.9</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -5950,10 +5914,10 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -5965,7 +5929,7 @@
         <v>96.7</v>
       </c>
       <c r="T8">
-        <v>52.9</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -5977,10 +5941,10 @@
         <v>100</v>
       </c>
       <c r="X8">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Z8">
         <v>100</v>
@@ -6024,7 +5988,7 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>64.7</v>
+        <v>80.8</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -6036,7 +6000,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -6051,7 +6015,7 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>64.7</v>
+        <v>80.8</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -6063,7 +6027,7 @@
         <v>100</v>
       </c>
       <c r="X9">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Y9">
         <v>100</v>
@@ -6110,7 +6074,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>58.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -6122,7 +6086,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -6137,7 +6101,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>58.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -6149,7 +6113,7 @@
         <v>100</v>
       </c>
       <c r="X10">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -6196,7 +6160,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>64.7</v>
+        <v>80.8</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -6208,13 +6172,13 @@
         <v>86.7</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -6223,7 +6187,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>64.7</v>
+        <v>80.8</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -6235,13 +6199,13 @@
         <v>86.7</v>
       </c>
       <c r="X11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Y11">
         <v>100</v>
       </c>
       <c r="Z11">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AA11">
         <v>100</v>
@@ -6282,7 +6246,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>64.7</v>
+        <v>80.8</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -6309,7 +6273,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>64.7</v>
+        <v>80.8</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -6368,7 +6332,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>64.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -6380,7 +6344,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -6395,7 +6359,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>64.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -6407,7 +6371,7 @@
         <v>100</v>
       </c>
       <c r="X13">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -6454,7 +6418,7 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -6466,7 +6430,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -6481,7 +6445,7 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -6493,7 +6457,7 @@
         <v>100</v>
       </c>
       <c r="X14">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y14">
         <v>100</v>
@@ -6540,7 +6504,7 @@
         <v>53.3</v>
       </c>
       <c r="K15">
-        <v>52.9</v>
+        <v>57.7</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -6552,22 +6516,22 @@
         <v>93.3</v>
       </c>
       <c r="O15">
-        <v>56.3</v>
+        <v>34.4</v>
       </c>
       <c r="P15">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q15">
-        <v>80</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="S15">
-        <v>53.3</v>
+        <v>70</v>
       </c>
       <c r="T15">
-        <v>52.9</v>
+        <v>57.7</v>
       </c>
       <c r="U15">
         <v>0</v>
@@ -6579,19 +6543,19 @@
         <v>93.3</v>
       </c>
       <c r="X15">
-        <v>56.3</v>
+        <v>34.4</v>
       </c>
       <c r="Y15">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Z15">
-        <v>80</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AA15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AB15">
-        <v>53.3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:28">
@@ -6626,7 +6590,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>70.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -6638,7 +6602,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -6653,7 +6617,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>70.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -6665,7 +6629,7 @@
         <v>100</v>
       </c>
       <c r="X16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y16">
         <v>100</v>
@@ -6712,7 +6676,7 @@
         <v>66.7</v>
       </c>
       <c r="K17">
-        <v>52.9</v>
+        <v>50</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -6724,22 +6688,22 @@
         <v>73.3</v>
       </c>
       <c r="O17">
-        <v>37.5</v>
+        <v>18.8</v>
       </c>
       <c r="P17">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="Q17">
-        <v>75</v>
+        <v>38.5</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="S17">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="T17">
-        <v>52.9</v>
+        <v>50</v>
       </c>
       <c r="U17">
         <v>0</v>
@@ -6751,19 +6715,19 @@
         <v>73.3</v>
       </c>
       <c r="X17">
-        <v>37.5</v>
+        <v>18.8</v>
       </c>
       <c r="Y17">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="Z17">
-        <v>75</v>
+        <v>38.5</v>
       </c>
       <c r="AA17">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AB17">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="18" spans="1:28">
@@ -6798,7 +6762,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>64.7</v>
+        <v>80.8</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -6810,13 +6774,13 @@
         <v>93.3</v>
       </c>
       <c r="O18">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -6825,7 +6789,7 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>64.7</v>
+        <v>80.8</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -6837,13 +6801,13 @@
         <v>93.3</v>
       </c>
       <c r="X18">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="Y18">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Z18">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AA18">
         <v>100</v>
@@ -6884,7 +6848,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>64.7</v>
+        <v>80.8</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -6896,7 +6860,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -6911,7 +6875,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>64.7</v>
+        <v>80.8</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -6923,7 +6887,7 @@
         <v>100</v>
       </c>
       <c r="X19">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y19">
         <v>100</v>
@@ -6970,19 +6934,19 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>58.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L20">
-        <v>84.2</v>
+        <v>87.5</v>
       </c>
       <c r="M20">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N20">
         <v>86.7</v>
       </c>
       <c r="O20">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -6994,22 +6958,22 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="T20">
-        <v>58.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U20">
-        <v>84.2</v>
+        <v>87.5</v>
       </c>
       <c r="V20">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W20">
         <v>86.7</v>
       </c>
       <c r="X20">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -7021,7 +6985,7 @@
         <v>100</v>
       </c>
       <c r="AB20">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="21" spans="1:28">
@@ -7032,7 +6996,7 @@
         <v>52.9</v>
       </c>
       <c r="C21">
-        <v>78.90000000000001</v>
+        <v>26.3</v>
       </c>
       <c r="D21">
         <v>50</v>
@@ -7056,10 +7020,10 @@
         <v>90</v>
       </c>
       <c r="K21">
-        <v>52.9</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L21">
-        <v>78.90000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="M21">
         <v>50</v>
@@ -7068,25 +7032,25 @@
         <v>93.3</v>
       </c>
       <c r="O21">
-        <v>62.5</v>
+        <v>40.6</v>
       </c>
       <c r="P21">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>79.5</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="S21">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="T21">
-        <v>52.9</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="U21">
-        <v>78.90000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="V21">
         <v>50</v>
@@ -7095,19 +7059,19 @@
         <v>93.3</v>
       </c>
       <c r="X21">
-        <v>62.5</v>
+        <v>40.6</v>
       </c>
       <c r="Y21">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="Z21">
-        <v>100</v>
+        <v>79.5</v>
       </c>
       <c r="AA21">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AB21">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:28">
@@ -7142,7 +7106,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>64.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -7154,7 +7118,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -7169,7 +7133,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>64.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -7181,7 +7145,7 @@
         <v>100</v>
       </c>
       <c r="X22">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y22">
         <v>100</v>
@@ -7228,10 +7192,10 @@
         <v>96.7</v>
       </c>
       <c r="K23">
-        <v>58.8</v>
+        <v>69.2</v>
       </c>
       <c r="L23">
-        <v>94.7</v>
+        <v>70</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -7240,25 +7204,25 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>96.7</v>
+        <v>90</v>
       </c>
       <c r="T23">
-        <v>58.8</v>
+        <v>69.2</v>
       </c>
       <c r="U23">
-        <v>94.7</v>
+        <v>70</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -7267,19 +7231,19 @@
         <v>100</v>
       </c>
       <c r="X23">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Y23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Z23">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AA23">
         <v>100</v>
       </c>
       <c r="AB23">
-        <v>96.7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:28">
@@ -7314,7 +7278,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>64.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -7332,7 +7296,7 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -7341,7 +7305,7 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>64.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -7359,7 +7323,7 @@
         <v>100</v>
       </c>
       <c r="Z24">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AA24">
         <v>100</v>
@@ -7400,7 +7364,7 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>58.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -7412,7 +7376,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -7427,7 +7391,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>58.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -7439,7 +7403,7 @@
         <v>100</v>
       </c>
       <c r="X25">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y25">
         <v>100</v>
@@ -7486,7 +7450,7 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>70.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -7498,7 +7462,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -7513,7 +7477,7 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>70.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -7525,7 +7489,7 @@
         <v>100</v>
       </c>
       <c r="X26">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Y26">
         <v>100</v>
@@ -7572,10 +7536,10 @@
         <v>93.3</v>
       </c>
       <c r="K27">
-        <v>64.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -7584,25 +7548,25 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P27">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="T27">
-        <v>64.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -7611,19 +7575,19 @@
         <v>100</v>
       </c>
       <c r="X27">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Y27">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Z27">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AA27">
         <v>100</v>
       </c>
       <c r="AB27">
-        <v>93.3</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:28">
@@ -7658,7 +7622,7 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>64.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -7670,7 +7634,7 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -7685,7 +7649,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>64.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -7697,7 +7661,7 @@
         <v>100</v>
       </c>
       <c r="X28">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y28">
         <v>100</v>
@@ -7744,7 +7708,7 @@
         <v>96.7</v>
       </c>
       <c r="K29">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -7756,13 +7720,13 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P29">
         <v>96</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -7771,7 +7735,7 @@
         <v>96.7</v>
       </c>
       <c r="T29">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -7783,13 +7747,13 @@
         <v>100</v>
       </c>
       <c r="X29">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Y29">
         <v>96</v>
       </c>
       <c r="Z29">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AA29">
         <v>100</v>
@@ -7845,7 +7809,7 @@
         <v>93.8</v>
       </c>
       <c r="P30">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -7872,7 +7836,7 @@
         <v>93.8</v>
       </c>
       <c r="Y30">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Z30">
         <v>100</v>
@@ -7916,7 +7880,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -7928,13 +7892,13 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P31">
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -7943,7 +7907,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -7955,13 +7919,13 @@
         <v>100</v>
       </c>
       <c r="X31">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y31">
         <v>100</v>
       </c>
       <c r="Z31">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AA31">
         <v>100</v>
@@ -8002,7 +7966,7 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>64.7</v>
+        <v>69.2</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -8014,22 +7978,22 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P32">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T32">
-        <v>64.7</v>
+        <v>69.2</v>
       </c>
       <c r="U32">
         <v>100</v>
@@ -8041,19 +8005,19 @@
         <v>100</v>
       </c>
       <c r="X32">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Y32">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Z32">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AA32">
         <v>100</v>
       </c>
       <c r="AB32">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:28">
@@ -8088,10 +8052,10 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>64.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M33">
         <v>100</v>
@@ -8100,13 +8064,13 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P33">
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R33">
         <v>100</v>
@@ -8115,10 +8079,10 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>64.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="U33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -8127,13 +8091,13 @@
         <v>100</v>
       </c>
       <c r="X33">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y33">
         <v>100</v>
       </c>
       <c r="Z33">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AA33">
         <v>100</v>
@@ -8174,7 +8138,7 @@
         <v>100</v>
       </c>
       <c r="K34">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -8201,7 +8165,7 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="U34">
         <v>100</v>
@@ -8260,7 +8224,7 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>64.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -8272,13 +8236,13 @@
         <v>100</v>
       </c>
       <c r="O35">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P35">
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="R35">
         <v>100</v>
@@ -8287,7 +8251,7 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>64.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U35">
         <v>100</v>
@@ -8299,13 +8263,13 @@
         <v>100</v>
       </c>
       <c r="X35">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y35">
         <v>100</v>
       </c>
       <c r="Z35">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="AA35">
         <v>100</v>
@@ -8346,7 +8310,7 @@
         <v>100</v>
       </c>
       <c r="K36">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L36">
         <v>100</v>
@@ -8358,7 +8322,7 @@
         <v>100</v>
       </c>
       <c r="O36">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P36">
         <v>100</v>
@@ -8373,7 +8337,7 @@
         <v>100</v>
       </c>
       <c r="T36">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="U36">
         <v>100</v>
@@ -8385,7 +8349,7 @@
         <v>100</v>
       </c>
       <c r="X36">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y36">
         <v>100</v>
@@ -8432,7 +8396,7 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L37">
         <v>100</v>
@@ -8444,7 +8408,7 @@
         <v>100</v>
       </c>
       <c r="O37">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P37">
         <v>100</v>
@@ -8459,7 +8423,7 @@
         <v>100</v>
       </c>
       <c r="T37">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="U37">
         <v>100</v>
@@ -8471,7 +8435,7 @@
         <v>100</v>
       </c>
       <c r="X37">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y37">
         <v>100</v>
@@ -8518,7 +8482,7 @@
         <v>100</v>
       </c>
       <c r="K38">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L38">
         <v>100</v>
@@ -8530,22 +8494,22 @@
         <v>100</v>
       </c>
       <c r="O38">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P38">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q38">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="R38">
         <v>100</v>
       </c>
       <c r="S38">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="T38">
-        <v>70.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="U38">
         <v>100</v>
@@ -8557,19 +8521,19 @@
         <v>100</v>
       </c>
       <c r="X38">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Y38">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Z38">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AA38">
         <v>100</v>
       </c>
       <c r="AB38">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="39" spans="1:28">
@@ -8604,10 +8568,10 @@
         <v>100</v>
       </c>
       <c r="K39">
-        <v>58.8</v>
+        <v>61.5</v>
       </c>
       <c r="L39">
-        <v>100</v>
+        <v>47.5</v>
       </c>
       <c r="M39">
         <v>100</v>
@@ -8616,25 +8580,25 @@
         <v>93.3</v>
       </c>
       <c r="O39">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P39">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q39">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R39">
         <v>100</v>
       </c>
       <c r="S39">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="T39">
-        <v>58.8</v>
+        <v>61.5</v>
       </c>
       <c r="U39">
-        <v>100</v>
+        <v>47.5</v>
       </c>
       <c r="V39">
         <v>100</v>
@@ -8643,19 +8607,19 @@
         <v>93.3</v>
       </c>
       <c r="X39">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Y39">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Z39">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AA39">
         <v>100</v>
       </c>
       <c r="AB39">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="40" spans="1:28">
@@ -8690,10 +8654,10 @@
         <v>100</v>
       </c>
       <c r="K40">
-        <v>47.1</v>
+        <v>61.5</v>
       </c>
       <c r="L40">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M40">
         <v>100</v>
@@ -8702,25 +8666,25 @@
         <v>100</v>
       </c>
       <c r="O40">
-        <v>87.5</v>
+        <v>75</v>
       </c>
       <c r="P40">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q40">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R40">
         <v>100</v>
       </c>
       <c r="S40">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="T40">
-        <v>47.1</v>
+        <v>61.5</v>
       </c>
       <c r="U40">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="V40">
         <v>100</v>
@@ -8729,19 +8693,19 @@
         <v>100</v>
       </c>
       <c r="X40">
-        <v>87.5</v>
+        <v>75</v>
       </c>
       <c r="Y40">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Z40">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AA40">
         <v>100</v>
       </c>
       <c r="AB40">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="41" spans="1:28">
@@ -8776,10 +8740,10 @@
         <v>100</v>
       </c>
       <c r="K41">
-        <v>58.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L41">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M41">
         <v>100</v>
@@ -8788,25 +8752,25 @@
         <v>100</v>
       </c>
       <c r="O41">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P41">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q41">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R41">
         <v>100</v>
       </c>
       <c r="S41">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="T41">
-        <v>58.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U41">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V41">
         <v>100</v>
@@ -8815,19 +8779,19 @@
         <v>100</v>
       </c>
       <c r="X41">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Y41">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Z41">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AA41">
         <v>100</v>
       </c>
       <c r="AB41">
-        <v>100</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="42" spans="1:28">
@@ -8862,7 +8826,7 @@
         <v>100</v>
       </c>
       <c r="K42">
-        <v>58.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L42">
         <v>100</v>
@@ -8874,13 +8838,13 @@
         <v>100</v>
       </c>
       <c r="O42">
-        <v>93.8</v>
+        <v>81.3</v>
       </c>
       <c r="P42">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q42">
-        <v>100</v>
+        <v>89.7</v>
       </c>
       <c r="R42">
         <v>100</v>
@@ -8889,7 +8853,7 @@
         <v>100</v>
       </c>
       <c r="T42">
-        <v>58.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="U42">
         <v>100</v>
@@ -8901,13 +8865,13 @@
         <v>100</v>
       </c>
       <c r="X42">
-        <v>93.8</v>
+        <v>81.3</v>
       </c>
       <c r="Y42">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Z42">
-        <v>100</v>
+        <v>89.7</v>
       </c>
       <c r="AA42">
         <v>100</v>
@@ -8999,7 +8963,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -9008,19 +8972,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2">
-        <v>69.2</v>
+        <v>66.7</v>
       </c>
       <c r="G3" s="2">
-        <v>30.8</v>
+        <v>33.3</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -9031,28 +8995,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4">
         <v>39</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2">
-        <v>76.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="G4" s="2">
-        <v>23.1</v>
+        <v>30.8</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -9063,28 +9027,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5">
         <v>39</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2">
-        <v>82.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="G5" s="2">
-        <v>17.9</v>
+        <v>28.2</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -9095,28 +9059,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6">
         <v>39</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2">
-        <v>82.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>17.9</v>
+        <v>25.6</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -9130,25 +9094,25 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7">
         <v>39</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2">
-        <v>84.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>15.4</v>
+        <v>23.1</v>
       </c>
       <c r="H7">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -9159,28 +9123,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8">
         <v>39</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2">
-        <v>84.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="G8" s="2">
-        <v>15.4</v>
+        <v>10.3</v>
       </c>
       <c r="H8">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -9244,7 +9208,7 @@
         <v>7.7</v>
       </c>
       <c r="H10">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -9294,7 +9258,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9326,19 +9290,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920080</v>
+        <v>23330051920234</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>68</v>
@@ -9349,16 +9313,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920080</v>
+        <v>23330051920234</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -9372,19 +9336,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920261</v>
+        <v>23330051920103</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>67</v>
@@ -9395,16 +9359,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920261</v>
+        <v>23330051920103</v>
       </c>
       <c r="B5" t="s">
         <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -9424,16 +9388,16 @@
         <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -9447,10 +9411,10 @@
         <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -9464,39 +9428,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920112</v>
+        <v>23330051920078</v>
       </c>
       <c r="B8" t="s">
         <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920112</v>
+        <v>23330051920077</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -9510,39 +9474,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920114</v>
+        <v>23330051920082</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920114</v>
+        <v>23330051920085</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -9556,39 +9520,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920115</v>
+        <v>23330051920086</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920115</v>
+        <v>23330051920084</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -9602,16 +9566,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920078</v>
+        <v>23330051920087</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
@@ -9625,16 +9589,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920077</v>
+        <v>23330051920088</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -9648,16 +9612,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920082</v>
+        <v>23330051920089</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
@@ -9671,16 +9635,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920085</v>
+        <v>23330051920091</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
@@ -9694,16 +9658,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920086</v>
+        <v>23330051920094</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E18" t="s">
         <v>12</v>
@@ -9717,16 +9681,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920084</v>
+        <v>23330051920251</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
@@ -9740,16 +9704,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920087</v>
+        <v>23330051920099</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>
@@ -9763,16 +9727,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920088</v>
+        <v>23330051920098</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
@@ -9786,16 +9750,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920089</v>
+        <v>23330051920100</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E22" t="s">
         <v>12</v>
@@ -9809,16 +9773,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920091</v>
+        <v>23330051920102</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
@@ -9832,16 +9796,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920094</v>
+        <v>23330051920104</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E24" t="s">
         <v>12</v>
@@ -9855,16 +9819,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920251</v>
+        <v>23330051920106</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E25" t="s">
         <v>12</v>
@@ -9878,16 +9842,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920099</v>
+        <v>23330051920108</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E26" t="s">
         <v>12</v>
@@ -9901,16 +9865,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920098</v>
+        <v>23330051920110</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E27" t="s">
         <v>12</v>
@@ -9924,16 +9888,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920100</v>
+        <v>23330051920111</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E28" t="s">
         <v>12</v>
@@ -9942,167 +9906,6 @@
         <v>66</v>
       </c>
       <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>23330051920102</v>
-      </c>
-      <c r="B29" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" t="s">
-        <v>146</v>
-      </c>
-      <c r="E29" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>23330051920104</v>
-      </c>
-      <c r="B30" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" t="s">
-        <v>147</v>
-      </c>
-      <c r="E30" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" t="s">
-        <v>66</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>23330051920105</v>
-      </c>
-      <c r="B31" t="s">
-        <v>100</v>
-      </c>
-      <c r="C31" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" t="s">
-        <v>148</v>
-      </c>
-      <c r="E31" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>23330051920106</v>
-      </c>
-      <c r="B32" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" t="s">
-        <v>149</v>
-      </c>
-      <c r="E32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" t="s">
-        <v>66</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>23330051920108</v>
-      </c>
-      <c r="B33" t="s">
-        <v>102</v>
-      </c>
-      <c r="C33" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" t="s">
-        <v>150</v>
-      </c>
-      <c r="E33" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" t="s">
-        <v>66</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>23330051920110</v>
-      </c>
-      <c r="B34" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" t="s">
-        <v>124</v>
-      </c>
-      <c r="D34" t="s">
-        <v>151</v>
-      </c>
-      <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" t="s">
-        <v>66</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>23330051920111</v>
-      </c>
-      <c r="B35" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" t="s">
-        <v>87</v>
-      </c>
-      <c r="D35" t="s">
-        <v>152</v>
-      </c>
-      <c r="E35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" t="s">
-        <v>66</v>
-      </c>
-      <c r="G35">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ALCM - Estadisticos 20232.xlsx
+++ b/grupos/2ALCM - Estadisticos 20232.xlsx
@@ -1014,7 +1014,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>7</v>
@@ -1127,7 +1127,7 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>10</v>
@@ -1240,7 +1240,7 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -1294,7 +1294,7 @@
         <v>8</v>
       </c>
       <c r="AF6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG6">
         <v>9</v>
@@ -1353,7 +1353,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
         <v>9</v>
@@ -1466,7 +1466,7 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>5</v>
@@ -1579,7 +1579,7 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>8</v>
@@ -1692,7 +1692,7 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -1746,7 +1746,7 @@
         <v>8</v>
       </c>
       <c r="AF10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1805,7 +1805,7 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>8</v>
@@ -1859,7 +1859,7 @@
         <v>9</v>
       </c>
       <c r="AF11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG11">
         <v>9</v>
@@ -1918,7 +1918,7 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
         <v>10</v>
@@ -2031,7 +2031,7 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>10</v>
@@ -2144,7 +2144,7 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>10</v>
@@ -2198,7 +2198,7 @@
         <v>9</v>
       </c>
       <c r="AF14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG14">
         <v>9</v>
@@ -2257,7 +2257,7 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>5</v>
@@ -2370,7 +2370,7 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>10</v>
@@ -2483,7 +2483,7 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -2596,7 +2596,7 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>9</v>
@@ -2650,7 +2650,7 @@
         <v>8</v>
       </c>
       <c r="AF18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2709,7 +2709,7 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>8</v>
@@ -2822,7 +2822,7 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>7</v>
@@ -2876,7 +2876,7 @@
         <v>6</v>
       </c>
       <c r="AF20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG20">
         <v>8</v>
@@ -2935,7 +2935,7 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>5</v>
@@ -3048,7 +3048,7 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>7</v>
@@ -3161,7 +3161,7 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>7</v>
@@ -3215,7 +3215,7 @@
         <v>5</v>
       </c>
       <c r="AF23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG23">
         <v>8</v>
@@ -3274,7 +3274,7 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>8</v>
@@ -3387,7 +3387,7 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
         <v>9</v>
@@ -3500,7 +3500,7 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>8</v>
@@ -3613,7 +3613,7 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>5</v>
@@ -3667,7 +3667,7 @@
         <v>7</v>
       </c>
       <c r="AF27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG27">
         <v>7</v>
@@ -3726,7 +3726,7 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>10</v>
@@ -3780,7 +3780,7 @@
         <v>8</v>
       </c>
       <c r="AF28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG28">
         <v>9</v>
@@ -3839,7 +3839,7 @@
         <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>7</v>
@@ -3893,7 +3893,7 @@
         <v>9</v>
       </c>
       <c r="AF29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG29">
         <v>9</v>
@@ -3952,7 +3952,7 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
         <v>9</v>
@@ -4065,7 +4065,7 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>10</v>
@@ -4178,7 +4178,7 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
         <v>5</v>
@@ -4291,7 +4291,7 @@
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
         <v>8</v>
@@ -4345,7 +4345,7 @@
         <v>8</v>
       </c>
       <c r="AF33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG33">
         <v>9</v>
@@ -4404,7 +4404,7 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>10</v>
@@ -4517,7 +4517,7 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
         <v>8</v>
@@ -4571,7 +4571,7 @@
         <v>8</v>
       </c>
       <c r="AF35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG35">
         <v>9</v>
@@ -4630,7 +4630,7 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>10</v>
@@ -4743,7 +4743,7 @@
         <v>8</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
         <v>9</v>
@@ -4797,7 +4797,7 @@
         <v>9</v>
       </c>
       <c r="AF37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG37">
         <v>10</v>
@@ -4856,7 +4856,7 @@
         <v>7</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
         <v>10</v>
@@ -4969,7 +4969,7 @@
         <v>6</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>5</v>
@@ -5082,7 +5082,7 @@
         <v>7</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O40">
         <v>5</v>
@@ -5195,7 +5195,7 @@
         <v>7</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O41">
         <v>10</v>
@@ -5308,7 +5308,7 @@
         <v>6</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>5</v>
@@ -5739,7 +5739,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O6">
         <v>96.90000000000001</v>
@@ -5766,7 +5766,7 @@
         <v>100</v>
       </c>
       <c r="W6">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X6">
         <v>96.90000000000001</v>
@@ -5825,7 +5825,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O7">
         <v>96.90000000000001</v>
@@ -5852,7 +5852,7 @@
         <v>100</v>
       </c>
       <c r="W7">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X7">
         <v>96.90000000000001</v>
@@ -5911,7 +5911,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O8">
         <v>90.59999999999999</v>
@@ -5938,7 +5938,7 @@
         <v>100</v>
       </c>
       <c r="W8">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X8">
         <v>90.59999999999999</v>
@@ -6169,7 +6169,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="O11">
         <v>93.8</v>
@@ -6196,7 +6196,7 @@
         <v>100</v>
       </c>
       <c r="W11">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="X11">
         <v>93.8</v>
@@ -6255,7 +6255,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O12">
         <v>87.5</v>
@@ -6282,7 +6282,7 @@
         <v>100</v>
       </c>
       <c r="W12">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X12">
         <v>87.5</v>
@@ -6513,7 +6513,7 @@
         <v>50</v>
       </c>
       <c r="N15">
-        <v>93.3</v>
+        <v>70</v>
       </c>
       <c r="O15">
         <v>34.4</v>
@@ -6540,7 +6540,7 @@
         <v>50</v>
       </c>
       <c r="W15">
-        <v>93.3</v>
+        <v>70</v>
       </c>
       <c r="X15">
         <v>34.4</v>
@@ -6685,7 +6685,7 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>73.3</v>
+        <v>36.7</v>
       </c>
       <c r="O17">
         <v>18.8</v>
@@ -6712,7 +6712,7 @@
         <v>100</v>
       </c>
       <c r="W17">
-        <v>73.3</v>
+        <v>36.7</v>
       </c>
       <c r="X17">
         <v>18.8</v>
@@ -6771,7 +6771,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>93.3</v>
+        <v>83.3</v>
       </c>
       <c r="O18">
         <v>93.8</v>
@@ -6798,7 +6798,7 @@
         <v>100</v>
       </c>
       <c r="W18">
-        <v>93.3</v>
+        <v>83.3</v>
       </c>
       <c r="X18">
         <v>93.8</v>
@@ -7029,7 +7029,7 @@
         <v>50</v>
       </c>
       <c r="N21">
-        <v>93.3</v>
+        <v>76.7</v>
       </c>
       <c r="O21">
         <v>40.6</v>
@@ -7056,7 +7056,7 @@
         <v>50</v>
       </c>
       <c r="W21">
-        <v>93.3</v>
+        <v>76.7</v>
       </c>
       <c r="X21">
         <v>40.6</v>
@@ -7115,7 +7115,7 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O22">
         <v>90.59999999999999</v>
@@ -7142,7 +7142,7 @@
         <v>100</v>
       </c>
       <c r="W22">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X22">
         <v>90.59999999999999</v>
@@ -7201,7 +7201,7 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O23">
         <v>93.8</v>
@@ -7228,7 +7228,7 @@
         <v>100</v>
       </c>
       <c r="W23">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X23">
         <v>93.8</v>
@@ -7287,7 +7287,7 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O24">
         <v>93.8</v>
@@ -7314,7 +7314,7 @@
         <v>100</v>
       </c>
       <c r="W24">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="X24">
         <v>93.8</v>
@@ -7545,7 +7545,7 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="O27">
         <v>84.40000000000001</v>
@@ -7572,7 +7572,7 @@
         <v>100</v>
       </c>
       <c r="W27">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="X27">
         <v>84.40000000000001</v>
@@ -7803,7 +7803,7 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O30">
         <v>93.8</v>
@@ -7830,7 +7830,7 @@
         <v>100</v>
       </c>
       <c r="W30">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X30">
         <v>93.8</v>
@@ -8233,7 +8233,7 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O35">
         <v>96.90000000000001</v>
@@ -8260,7 +8260,7 @@
         <v>100</v>
       </c>
       <c r="W35">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X35">
         <v>96.90000000000001</v>
@@ -8491,7 +8491,7 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O38">
         <v>93.8</v>
@@ -8518,7 +8518,7 @@
         <v>100</v>
       </c>
       <c r="W38">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X38">
         <v>93.8</v>
@@ -8577,7 +8577,7 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O39">
         <v>93.8</v>
@@ -8604,7 +8604,7 @@
         <v>100</v>
       </c>
       <c r="W39">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="X39">
         <v>93.8</v>
@@ -8663,7 +8663,7 @@
         <v>100</v>
       </c>
       <c r="N40">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O40">
         <v>75</v>
@@ -8690,7 +8690,7 @@
         <v>100</v>
       </c>
       <c r="W40">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X40">
         <v>75</v>
@@ -8835,7 +8835,7 @@
         <v>100</v>
       </c>
       <c r="N42">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="O42">
         <v>81.3</v>
@@ -8862,7 +8862,7 @@
         <v>100</v>
       </c>
       <c r="W42">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="X42">
         <v>81.3</v>
@@ -9164,19 +9164,19 @@
         <v>39</v>
       </c>
       <c r="D9">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="2">
-        <v>92.3</v>
+        <v>89.7</v>
       </c>
       <c r="G9" s="2">
-        <v>7.7</v>
+        <v>10.3</v>
       </c>
       <c r="H9">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="I9">
         <v>0</v>

--- a/grupos/2ALCM - Estadisticos 20232.xlsx
+++ b/grupos/2ALCM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="167">
   <si>
     <t>Materia</t>
   </si>
@@ -221,27 +221,27 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Sanchez Morales Gilberto</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Sanchez Morales Gilberto</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -254,96 +254,138 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>ALTAMIRA</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>AZPIRI</t>
+  </si>
+  <si>
+    <t>BONOLA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>ESCOBEDO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>PASTRANA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>ALTAMIRA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ESCOBEDO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
     <t>SEGURA</t>
   </si>
   <si>
     <t>SILVESTRE</t>
   </si>
   <si>
-    <t>TEXOCO</t>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>VANEGAS</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VARILLAS</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>CARPINTEYRO</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
   </si>
   <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>VARILLAS</t>
-  </si>
-  <si>
-    <t>CARPINTEYRO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
@@ -362,6 +404,9 @@
     <t>BERISTAIN</t>
   </si>
   <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
     <t>TEZOCO</t>
   </si>
   <si>
@@ -371,69 +416,96 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>MIXTECO</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>ARIATNA</t>
+  </si>
+  <si>
+    <t>MELANY</t>
+  </si>
+  <si>
+    <t>MARGARITA</t>
+  </si>
+  <si>
+    <t>LINET</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>ANGEL NAIN</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>OSWALDO</t>
+  </si>
+  <si>
+    <t>JANETH</t>
+  </si>
+  <si>
+    <t>ILSE JIMENA</t>
+  </si>
+  <si>
+    <t>DAYANA ASTRID</t>
+  </si>
+  <si>
+    <t>MARIAM MICHAELL</t>
+  </si>
+  <si>
+    <t>LAURA ISABEL</t>
+  </si>
+  <si>
+    <t>VIRIDIANA</t>
+  </si>
+  <si>
     <t>ALEX TADEO</t>
   </si>
   <si>
+    <t>YEIMI ALEXANDER</t>
+  </si>
+  <si>
+    <t>DIEGO GREGORIO</t>
+  </si>
+  <si>
+    <t>ANGEL EDUC</t>
+  </si>
+  <si>
+    <t>AXEL JOSUE</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>REY</t>
+  </si>
+  <si>
     <t>ARELI DANAE</t>
   </si>
   <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ANIELA SAMANTA</t>
+  </si>
+  <si>
+    <t>CONCEPCION GUADALUPE</t>
+  </si>
+  <si>
     <t>MIRANDA</t>
   </si>
   <si>
-    <t>LINET</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>OSWALDO</t>
-  </si>
-  <si>
-    <t>JANETH</t>
-  </si>
-  <si>
-    <t>ILSE JIMENA</t>
-  </si>
-  <si>
-    <t>DAYANA ASTRID</t>
-  </si>
-  <si>
-    <t>MARIAM MICHAELL</t>
-  </si>
-  <si>
-    <t>LAURA ISABEL</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>YEIMI ALEXANDER</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
-    <t>ANGEL EDUC</t>
-  </si>
-  <si>
-    <t>AXEL JOSUE</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>REY</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>CONCEPCION GUADALUPE</t>
-  </si>
-  <si>
     <t>DAFNE</t>
   </si>
   <si>
@@ -441,6 +513,12 @@
   </si>
   <si>
     <t>ARIADNA JARETZI</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>GUADALUPE ANAHI</t>
   </si>
 </sst>
 </file>
@@ -1032,31 +1110,31 @@
         <v>7</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>8</v>
@@ -1074,7 +1152,7 @@
         <v>8</v>
       </c>
       <c r="AH4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI4">
         <v>7</v>
@@ -1083,7 +1161,7 @@
         <v>-1</v>
       </c>
       <c r="AK4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1145,40 +1223,40 @@
         <v>7</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>10</v>
       </c>
       <c r="AD5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF5">
         <v>10</v>
@@ -1187,10 +1265,10 @@
         <v>10</v>
       </c>
       <c r="AH5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ5">
         <v>-1</v>
@@ -1258,37 +1336,37 @@
         <v>4</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC6">
         <v>7</v>
       </c>
       <c r="AD6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE6">
         <v>8</v>
@@ -1300,16 +1378,16 @@
         <v>9</v>
       </c>
       <c r="AH6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ6">
         <v>-1</v>
       </c>
       <c r="AK6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1371,34 +1449,34 @@
         <v>5</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD7">
         <v>6</v>
@@ -1407,7 +1485,7 @@
         <v>7</v>
       </c>
       <c r="AF7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG7">
         <v>9</v>
@@ -1422,7 +1500,7 @@
         <v>-1</v>
       </c>
       <c r="AK7">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1484,34 +1562,34 @@
         <v>7</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD8">
         <v>7</v>
@@ -1523,19 +1601,19 @@
         <v>6</v>
       </c>
       <c r="AG8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ8">
         <v>-1</v>
       </c>
       <c r="AK8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1597,37 +1675,37 @@
         <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE9">
         <v>8</v>
@@ -1639,7 +1717,7 @@
         <v>9</v>
       </c>
       <c r="AH9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI9">
         <v>9</v>
@@ -1648,7 +1726,7 @@
         <v>-1</v>
       </c>
       <c r="AK9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1710,31 +1788,31 @@
         <v>6</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -1749,19 +1827,19 @@
         <v>8</v>
       </c>
       <c r="AG10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ10">
         <v>-1</v>
       </c>
       <c r="AK10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1823,34 +1901,34 @@
         <v>7</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD11">
         <v>9</v>
@@ -1936,34 +2014,34 @@
         <v>8</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD12">
         <v>6</v>
@@ -1978,7 +2056,7 @@
         <v>10</v>
       </c>
       <c r="AH12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI12">
         <v>6</v>
@@ -1987,7 +2065,7 @@
         <v>-1</v>
       </c>
       <c r="AK12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2049,31 +2127,31 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -2162,40 +2240,40 @@
         <v>6</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD14">
         <v>6</v>
       </c>
       <c r="AE14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF14">
         <v>8</v>
@@ -2204,7 +2282,7 @@
         <v>9</v>
       </c>
       <c r="AH14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI14">
         <v>6</v>
@@ -2213,7 +2291,7 @@
         <v>-1</v>
       </c>
       <c r="AK14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2275,31 +2353,31 @@
         <v>4</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -2388,37 +2466,37 @@
         <v>8</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE16">
         <v>9</v>
@@ -2430,7 +2508,7 @@
         <v>10</v>
       </c>
       <c r="AH16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI16">
         <v>9</v>
@@ -2439,7 +2517,7 @@
         <v>-1</v>
       </c>
       <c r="AK16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2501,31 +2579,31 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC17">
         <v>5</v>
@@ -2614,52 +2692,52 @@
         <v>7</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE18">
         <v>8</v>
       </c>
       <c r="AF18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG18">
         <v>10</v>
       </c>
       <c r="AH18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ18">
         <v>-1</v>
@@ -2727,37 +2805,37 @@
         <v>6</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE19">
         <v>8</v>
@@ -2772,7 +2850,7 @@
         <v>8</v>
       </c>
       <c r="AI19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ19">
         <v>-1</v>
@@ -2840,37 +2918,37 @@
         <v>5</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC20">
         <v>6</v>
       </c>
       <c r="AD20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE20">
         <v>6</v>
@@ -2882,7 +2960,7 @@
         <v>8</v>
       </c>
       <c r="AH20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI20">
         <v>6</v>
@@ -2953,31 +3031,31 @@
         <v>4</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -3066,46 +3144,46 @@
         <v>9</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>8</v>
       </c>
       <c r="AD22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH22">
         <v>8</v>
@@ -3179,31 +3257,31 @@
         <v>4</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC23">
         <v>5</v>
@@ -3212,16 +3290,16 @@
         <v>5</v>
       </c>
       <c r="AE23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI23">
         <v>5</v>
@@ -3230,7 +3308,7 @@
         <v>-1</v>
       </c>
       <c r="AK23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -3292,31 +3370,31 @@
         <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC24">
         <v>7</v>
@@ -3405,34 +3483,34 @@
         <v>6</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD25">
         <v>9</v>
@@ -3450,7 +3528,7 @@
         <v>9</v>
       </c>
       <c r="AI25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ25">
         <v>-1</v>
@@ -3518,40 +3596,40 @@
         <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF26">
         <v>8</v>
@@ -3560,7 +3638,7 @@
         <v>9</v>
       </c>
       <c r="AH26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI26">
         <v>8</v>
@@ -3631,46 +3709,46 @@
         <v>4</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH27">
         <v>7</v>
@@ -3682,7 +3760,7 @@
         <v>-1</v>
       </c>
       <c r="AK27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:37">
@@ -3744,31 +3822,31 @@
         <v>6</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC28">
         <v>7</v>
@@ -3795,7 +3873,7 @@
         <v>-1</v>
       </c>
       <c r="AK28">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:37">
@@ -3857,49 +3935,49 @@
         <v>9</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC29">
         <v>9</v>
       </c>
       <c r="AD29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG29">
         <v>9</v>
       </c>
       <c r="AH29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI29">
         <v>7</v>
@@ -3970,37 +4048,37 @@
         <v>7</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC30">
         <v>7</v>
       </c>
       <c r="AD30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE30">
         <v>7</v>
@@ -4012,7 +4090,7 @@
         <v>9</v>
       </c>
       <c r="AH30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI30">
         <v>8</v>
@@ -4021,7 +4099,7 @@
         <v>-1</v>
       </c>
       <c r="AK30">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -4083,31 +4161,31 @@
         <v>9</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC31">
         <v>8</v>
@@ -4116,7 +4194,7 @@
         <v>7</v>
       </c>
       <c r="AE31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF31">
         <v>8</v>
@@ -4125,7 +4203,7 @@
         <v>10</v>
       </c>
       <c r="AH31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI31">
         <v>9</v>
@@ -4134,7 +4212,7 @@
         <v>-1</v>
       </c>
       <c r="AK31">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:37">
@@ -4196,49 +4274,49 @@
         <v>4</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD32">
         <v>6</v>
       </c>
       <c r="AE32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI32">
         <v>5</v>
@@ -4247,7 +4325,7 @@
         <v>-1</v>
       </c>
       <c r="AK32">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:37">
@@ -4309,43 +4387,43 @@
         <v>8</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE33">
         <v>8</v>
       </c>
       <c r="AF33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG33">
         <v>9</v>
@@ -4422,31 +4500,31 @@
         <v>10</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC34">
         <v>10</v>
@@ -4455,7 +4533,7 @@
         <v>9</v>
       </c>
       <c r="AE34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF34">
         <v>10</v>
@@ -4535,37 +4613,37 @@
         <v>6</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE35">
         <v>8</v>
@@ -4580,13 +4658,13 @@
         <v>9</v>
       </c>
       <c r="AI35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ35">
         <v>-1</v>
       </c>
       <c r="AK35">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:37">
@@ -4648,31 +4726,31 @@
         <v>9</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC36">
         <v>10</v>
@@ -4761,34 +4839,34 @@
         <v>6</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD37">
         <v>7</v>
@@ -4797,7 +4875,7 @@
         <v>9</v>
       </c>
       <c r="AF37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG37">
         <v>10</v>
@@ -4806,7 +4884,7 @@
         <v>8</v>
       </c>
       <c r="AI37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ37">
         <v>-1</v>
@@ -4874,31 +4952,31 @@
         <v>9</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC38">
         <v>9</v>
@@ -4913,7 +4991,7 @@
         <v>9</v>
       </c>
       <c r="AG38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH38">
         <v>7</v>
@@ -4925,7 +5003,7 @@
         <v>-1</v>
       </c>
       <c r="AK38">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:37">
@@ -4987,31 +5065,31 @@
         <v>4</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC39">
         <v>5</v>
@@ -5020,16 +5098,16 @@
         <v>6</v>
       </c>
       <c r="AE39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG39">
         <v>7</v>
       </c>
       <c r="AH39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI39">
         <v>6</v>
@@ -5038,7 +5116,7 @@
         <v>-1</v>
       </c>
       <c r="AK39">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:37">
@@ -5100,37 +5178,37 @@
         <v>4</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC40">
         <v>5</v>
       </c>
       <c r="AD40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE40">
         <v>6</v>
@@ -5139,10 +5217,10 @@
         <v>6</v>
       </c>
       <c r="AG40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI40">
         <v>5</v>
@@ -5151,7 +5229,7 @@
         <v>-1</v>
       </c>
       <c r="AK40">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:37">
@@ -5213,31 +5291,31 @@
         <v>4</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC41">
         <v>7</v>
@@ -5252,10 +5330,10 @@
         <v>8</v>
       </c>
       <c r="AG41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI41">
         <v>8</v>
@@ -5264,7 +5342,7 @@
         <v>-1</v>
       </c>
       <c r="AK41">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:37">
@@ -5326,52 +5404,52 @@
         <v>9</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC42">
         <v>7</v>
       </c>
       <c r="AD42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG42">
         <v>7</v>
       </c>
       <c r="AH42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ42">
         <v>-1</v>
@@ -5585,7 +5663,7 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>84.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -5597,7 +5675,7 @@
         <v>100</v>
       </c>
       <c r="X4">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y4">
         <v>100</v>
@@ -5671,7 +5749,7 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>84.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="U5">
         <v>100</v>
@@ -5757,7 +5835,7 @@
         <v>95</v>
       </c>
       <c r="T6">
-        <v>84.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -5766,22 +5844,22 @@
         <v>100</v>
       </c>
       <c r="W6">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="X6">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y6">
-        <v>90</v>
+        <v>91.3</v>
       </c>
       <c r="Z6">
-        <v>97.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA6">
         <v>100</v>
       </c>
       <c r="AB6">
-        <v>95</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="7" spans="1:28">
@@ -5843,7 +5921,7 @@
         <v>94.2</v>
       </c>
       <c r="T7">
-        <v>69.2</v>
+        <v>94.3</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -5852,22 +5930,22 @@
         <v>100</v>
       </c>
       <c r="W7">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="X7">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y7">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Z7">
-        <v>97.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="AA7">
         <v>100</v>
       </c>
       <c r="AB7">
-        <v>94.2</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="8" spans="1:28">
@@ -5929,7 +6007,7 @@
         <v>96.7</v>
       </c>
       <c r="T8">
-        <v>73.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -5938,22 +6016,22 @@
         <v>100</v>
       </c>
       <c r="W8">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="X8">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Y8">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="Z8">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA8">
         <v>100</v>
       </c>
       <c r="AB8">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:28">
@@ -6015,7 +6093,7 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>80.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -6027,7 +6105,7 @@
         <v>100</v>
       </c>
       <c r="X9">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y9">
         <v>100</v>
@@ -6101,7 +6179,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>76.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -6113,7 +6191,7 @@
         <v>100</v>
       </c>
       <c r="X10">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -6187,7 +6265,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>80.8</v>
+        <v>94.3</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -6196,16 +6274,16 @@
         <v>100</v>
       </c>
       <c r="W11">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="X11">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y11">
         <v>100</v>
       </c>
       <c r="Z11">
-        <v>94.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AA11">
         <v>100</v>
@@ -6273,7 +6351,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>80.8</v>
+        <v>94.3</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -6282,10 +6360,10 @@
         <v>100</v>
       </c>
       <c r="W12">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="X12">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="Y12">
         <v>100</v>
@@ -6359,7 +6437,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>76.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -6371,7 +6449,7 @@
         <v>100</v>
       </c>
       <c r="X13">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -6445,7 +6523,7 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>84.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -6457,7 +6535,7 @@
         <v>100</v>
       </c>
       <c r="X14">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y14">
         <v>100</v>
@@ -6531,7 +6609,7 @@
         <v>70</v>
       </c>
       <c r="T15">
-        <v>57.7</v>
+        <v>42.9</v>
       </c>
       <c r="U15">
         <v>0</v>
@@ -6540,22 +6618,22 @@
         <v>50</v>
       </c>
       <c r="W15">
-        <v>70</v>
+        <v>43.8</v>
       </c>
       <c r="X15">
-        <v>34.4</v>
+        <v>22.9</v>
       </c>
       <c r="Y15">
-        <v>74</v>
+        <v>46.3</v>
       </c>
       <c r="Z15">
-        <v>76.90000000000001</v>
+        <v>47.6</v>
       </c>
       <c r="AA15">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="AB15">
-        <v>70</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="16" spans="1:28">
@@ -6617,7 +6695,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>80.8</v>
+        <v>94.3</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -6629,7 +6707,7 @@
         <v>100</v>
       </c>
       <c r="X16">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y16">
         <v>100</v>
@@ -6703,7 +6781,7 @@
         <v>33.3</v>
       </c>
       <c r="T17">
-        <v>50</v>
+        <v>37.1</v>
       </c>
       <c r="U17">
         <v>0</v>
@@ -6712,22 +6790,22 @@
         <v>100</v>
       </c>
       <c r="W17">
-        <v>36.7</v>
+        <v>22.9</v>
       </c>
       <c r="X17">
-        <v>18.8</v>
+        <v>12.5</v>
       </c>
       <c r="Y17">
-        <v>36</v>
+        <v>22.5</v>
       </c>
       <c r="Z17">
-        <v>38.5</v>
+        <v>23.8</v>
       </c>
       <c r="AA17">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="AB17">
-        <v>33.3</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="18" spans="1:28">
@@ -6789,7 +6867,7 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>80.8</v>
+        <v>94.3</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -6798,16 +6876,16 @@
         <v>100</v>
       </c>
       <c r="W18">
-        <v>83.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X18">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y18">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Z18">
-        <v>97.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AA18">
         <v>100</v>
@@ -6875,7 +6953,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>80.8</v>
+        <v>94.3</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -6884,10 +6962,10 @@
         <v>100</v>
       </c>
       <c r="W19">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="X19">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Y19">
         <v>100</v>
@@ -6961,19 +7039,19 @@
         <v>98.3</v>
       </c>
       <c r="T20">
-        <v>76.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="U20">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="V20">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="W20">
-        <v>86.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="X20">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -6985,7 +7063,7 @@
         <v>100</v>
       </c>
       <c r="AB20">
-        <v>98.3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:28">
@@ -7047,31 +7125,31 @@
         <v>70</v>
       </c>
       <c r="T21">
-        <v>65.40000000000001</v>
+        <v>48.6</v>
       </c>
       <c r="U21">
-        <v>22.5</v>
+        <v>14.5</v>
       </c>
       <c r="V21">
         <v>50</v>
       </c>
       <c r="W21">
-        <v>76.7</v>
+        <v>47.9</v>
       </c>
       <c r="X21">
-        <v>40.6</v>
+        <v>27.1</v>
       </c>
       <c r="Y21">
-        <v>54</v>
+        <v>33.8</v>
       </c>
       <c r="Z21">
-        <v>79.5</v>
+        <v>49.2</v>
       </c>
       <c r="AA21">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="AB21">
-        <v>70</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="22" spans="1:28">
@@ -7133,7 +7211,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>76.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -7142,16 +7220,16 @@
         <v>100</v>
       </c>
       <c r="W22">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="X22">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Y22">
         <v>100</v>
       </c>
       <c r="Z22">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA22">
         <v>100</v>
@@ -7219,31 +7297,31 @@
         <v>90</v>
       </c>
       <c r="T23">
-        <v>69.2</v>
+        <v>51.4</v>
       </c>
       <c r="U23">
-        <v>70</v>
+        <v>74.2</v>
       </c>
       <c r="V23">
         <v>100</v>
       </c>
       <c r="W23">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="X23">
+        <v>91.7</v>
+      </c>
+      <c r="Y23">
         <v>93.8</v>
       </c>
-      <c r="Y23">
-        <v>90</v>
-      </c>
       <c r="Z23">
-        <v>97.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AA23">
         <v>100</v>
       </c>
       <c r="AB23">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="24" spans="1:28">
@@ -7305,7 +7383,7 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>76.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -7314,16 +7392,16 @@
         <v>100</v>
       </c>
       <c r="W24">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X24">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y24">
         <v>100</v>
       </c>
       <c r="Z24">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AA24">
         <v>100</v>
@@ -7391,7 +7469,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>73.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -7403,7 +7481,7 @@
         <v>100</v>
       </c>
       <c r="X25">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y25">
         <v>100</v>
@@ -7477,7 +7555,7 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>80.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -7489,7 +7567,7 @@
         <v>100</v>
       </c>
       <c r="X26">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y26">
         <v>100</v>
@@ -7563,31 +7641,31 @@
         <v>95</v>
       </c>
       <c r="T27">
-        <v>76.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="U27">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="V27">
         <v>100</v>
       </c>
       <c r="W27">
-        <v>86.7</v>
+        <v>87.5</v>
       </c>
       <c r="X27">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Y27">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="Z27">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AA27">
         <v>100</v>
       </c>
       <c r="AB27">
-        <v>95</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="28" spans="1:28">
@@ -7649,7 +7727,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>76.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -7661,7 +7739,7 @@
         <v>100</v>
       </c>
       <c r="X28">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y28">
         <v>100</v>
@@ -7735,7 +7813,7 @@
         <v>96.7</v>
       </c>
       <c r="T29">
-        <v>84.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -7747,19 +7825,19 @@
         <v>100</v>
       </c>
       <c r="X29">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y29">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Z29">
-        <v>97.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA29">
         <v>100</v>
       </c>
       <c r="AB29">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:28">
@@ -7830,13 +7908,13 @@
         <v>100</v>
       </c>
       <c r="W30">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="X30">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Y30">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="Z30">
         <v>100</v>
@@ -7845,7 +7923,7 @@
         <v>100</v>
       </c>
       <c r="AB30">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:28">
@@ -7907,7 +7985,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>84.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -7919,13 +7997,13 @@
         <v>100</v>
       </c>
       <c r="X31">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y31">
         <v>100</v>
       </c>
       <c r="Z31">
-        <v>97.40000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AA31">
         <v>100</v>
@@ -7993,7 +8071,7 @@
         <v>95</v>
       </c>
       <c r="T32">
-        <v>69.2</v>
+        <v>94.3</v>
       </c>
       <c r="U32">
         <v>100</v>
@@ -8005,19 +8083,19 @@
         <v>100</v>
       </c>
       <c r="X32">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Y32">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Z32">
-        <v>97.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AA32">
         <v>100</v>
       </c>
       <c r="AB32">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:28">
@@ -8079,10 +8157,10 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>73.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="U33">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -8091,13 +8169,13 @@
         <v>100</v>
       </c>
       <c r="X33">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Y33">
         <v>100</v>
       </c>
       <c r="Z33">
-        <v>97.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AA33">
         <v>100</v>
@@ -8165,7 +8243,7 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>84.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="U34">
         <v>100</v>
@@ -8251,7 +8329,7 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>76.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="U35">
         <v>100</v>
@@ -8260,16 +8338,16 @@
         <v>100</v>
       </c>
       <c r="W35">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X35">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y35">
         <v>100</v>
       </c>
       <c r="Z35">
-        <v>92.3</v>
+        <v>95.2</v>
       </c>
       <c r="AA35">
         <v>100</v>
@@ -8337,7 +8415,7 @@
         <v>100</v>
       </c>
       <c r="T36">
-        <v>84.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="U36">
         <v>100</v>
@@ -8349,7 +8427,7 @@
         <v>100</v>
       </c>
       <c r="X36">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y36">
         <v>100</v>
@@ -8423,7 +8501,7 @@
         <v>100</v>
       </c>
       <c r="T37">
-        <v>84.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="U37">
         <v>100</v>
@@ -8435,7 +8513,7 @@
         <v>100</v>
       </c>
       <c r="X37">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y37">
         <v>100</v>
@@ -8509,7 +8587,7 @@
         <v>98.3</v>
       </c>
       <c r="T38">
-        <v>84.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="U38">
         <v>100</v>
@@ -8518,22 +8596,22 @@
         <v>100</v>
       </c>
       <c r="W38">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="X38">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="Y38">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Z38">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AA38">
         <v>100</v>
       </c>
       <c r="AB38">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:28">
@@ -8571,7 +8649,7 @@
         <v>61.5</v>
       </c>
       <c r="L39">
-        <v>47.5</v>
+        <v>100</v>
       </c>
       <c r="M39">
         <v>100</v>
@@ -8595,31 +8673,31 @@
         <v>98.3</v>
       </c>
       <c r="T39">
-        <v>61.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="U39">
-        <v>47.5</v>
+        <v>100</v>
       </c>
       <c r="V39">
         <v>100</v>
       </c>
       <c r="W39">
-        <v>96.7</v>
+        <v>93.8</v>
       </c>
       <c r="X39">
         <v>93.8</v>
       </c>
       <c r="Y39">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Z39">
-        <v>97.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AA39">
         <v>100</v>
       </c>
       <c r="AB39">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:28">
@@ -8681,31 +8759,31 @@
         <v>98.3</v>
       </c>
       <c r="T40">
-        <v>61.5</v>
+        <v>74.3</v>
       </c>
       <c r="U40">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="V40">
         <v>100</v>
       </c>
       <c r="W40">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="X40">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Y40">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Z40">
-        <v>97.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="AA40">
         <v>100</v>
       </c>
       <c r="AB40">
-        <v>98.3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:28">
@@ -8767,31 +8845,31 @@
         <v>96.7</v>
       </c>
       <c r="T41">
-        <v>76.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="U41">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="V41">
+        <v>100</v>
+      </c>
+      <c r="W41">
+        <v>100</v>
+      </c>
+      <c r="X41">
+        <v>95.8</v>
+      </c>
+      <c r="Y41">
         <v>97.5</v>
       </c>
-      <c r="V41">
-        <v>100</v>
-      </c>
-      <c r="W41">
-        <v>100</v>
-      </c>
-      <c r="X41">
-        <v>93.8</v>
-      </c>
-      <c r="Y41">
-        <v>96</v>
-      </c>
       <c r="Z41">
-        <v>97.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA41">
         <v>100</v>
       </c>
       <c r="AB41">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:28">
@@ -8853,7 +8931,7 @@
         <v>100</v>
       </c>
       <c r="T42">
-        <v>73.09999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U42">
         <v>100</v>
@@ -8862,16 +8940,16 @@
         <v>100</v>
       </c>
       <c r="W42">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="X42">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Y42">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Z42">
-        <v>89.7</v>
+        <v>93.7</v>
       </c>
       <c r="AA42">
         <v>100</v>
@@ -8963,7 +9041,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -8972,19 +9050,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>66.7</v>
+        <v>79.5</v>
       </c>
       <c r="G3" s="2">
-        <v>33.3</v>
+        <v>20.5</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8995,28 +9073,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4">
         <v>39</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>69.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>30.8</v>
+        <v>15.4</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -9030,25 +9108,25 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5">
         <v>39</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>71.8</v>
+        <v>89.7</v>
       </c>
       <c r="G5" s="2">
-        <v>28.2</v>
+        <v>10.3</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -9059,28 +9137,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6">
         <v>39</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>74.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="G6" s="2">
-        <v>25.6</v>
+        <v>7.7</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -9091,28 +9169,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7">
         <v>39</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>76.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="G7" s="2">
-        <v>23.1</v>
+        <v>7.7</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -9123,28 +9201,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8">
         <v>39</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>89.7</v>
+        <v>92.3</v>
       </c>
       <c r="G8" s="2">
-        <v>10.3</v>
+        <v>7.7</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -9155,7 +9233,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>72</v>
@@ -9164,19 +9242,19 @@
         <v>39</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>89.7</v>
+        <v>92.3</v>
       </c>
       <c r="G9" s="2">
-        <v>10.3</v>
+        <v>7.7</v>
       </c>
       <c r="H9">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -9187,7 +9265,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
         <v>73</v>
@@ -9196,19 +9274,19 @@
         <v>39</v>
       </c>
       <c r="D10">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2">
-        <v>92.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="G10" s="2">
-        <v>7.7</v>
+        <v>5.1</v>
       </c>
       <c r="H10">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -9258,7 +9336,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9290,22 +9368,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920234</v>
+        <v>23330051920090</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -9313,16 +9391,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920234</v>
+        <v>23330051920090</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -9336,19 +9414,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920103</v>
+        <v>23330051920101</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
         <v>67</v>
@@ -9359,16 +9437,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920103</v>
+        <v>23330051920101</v>
       </c>
       <c r="B5" t="s">
         <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -9382,22 +9460,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920107</v>
+        <v>23330051920105</v>
       </c>
       <c r="B6" t="s">
         <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -9405,16 +9483,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920107</v>
+        <v>23330051920105</v>
       </c>
       <c r="B7" t="s">
         <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -9428,39 +9506,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920078</v>
+        <v>23330051920112</v>
       </c>
       <c r="B8" t="s">
         <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920077</v>
+        <v>23330051920112</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -9474,16 +9552,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920082</v>
+        <v>23330051920078</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -9497,16 +9575,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920085</v>
+        <v>23330051920077</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -9520,16 +9598,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920086</v>
+        <v>23330051920079</v>
       </c>
       <c r="B12" t="s">
         <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -9543,16 +9621,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920084</v>
+        <v>23330051920080</v>
       </c>
       <c r="B13" t="s">
         <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -9566,16 +9644,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920087</v>
+        <v>23330051920082</v>
       </c>
       <c r="B14" t="s">
         <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
@@ -9589,16 +9667,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920088</v>
+        <v>23330051920081</v>
       </c>
       <c r="B15" t="s">
         <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -9612,16 +9690,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920089</v>
+        <v>23330051920085</v>
       </c>
       <c r="B16" t="s">
         <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
@@ -9635,16 +9713,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920091</v>
+        <v>23330051920086</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
@@ -9658,16 +9736,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920094</v>
+        <v>23330051920084</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
         <v>12</v>
@@ -9681,16 +9759,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920251</v>
+        <v>23330051920087</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
@@ -9704,16 +9782,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920099</v>
+        <v>23330051920088</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>
@@ -9727,16 +9805,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920098</v>
+        <v>23330051920089</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
@@ -9750,16 +9828,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920100</v>
+        <v>23330051920091</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="E22" t="s">
         <v>12</v>
@@ -9773,16 +9851,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920102</v>
+        <v>23330051920234</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
@@ -9796,16 +9874,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920104</v>
+        <v>23330051920094</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="E24" t="s">
         <v>12</v>
@@ -9819,16 +9897,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920106</v>
+        <v>23330051920251</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="E25" t="s">
         <v>12</v>
@@ -9842,16 +9920,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920108</v>
+        <v>23330051920099</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="E26" t="s">
         <v>12</v>
@@ -9865,16 +9943,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920110</v>
+        <v>23330051920098</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="E27" t="s">
         <v>12</v>
@@ -9888,16 +9966,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920111</v>
+        <v>23330051920100</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="E28" t="s">
         <v>12</v>
@@ -9906,6 +9984,259 @@
         <v>66</v>
       </c>
       <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>23330051920102</v>
+      </c>
+      <c r="B29" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>66</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>23330051920103</v>
+      </c>
+      <c r="B30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" t="s">
+        <v>157</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>23330051920104</v>
+      </c>
+      <c r="B31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" t="s">
+        <v>158</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>66</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>23330051920261</v>
+      </c>
+      <c r="B32" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" t="s">
+        <v>159</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>66</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>23330051920106</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33" t="s">
+        <v>160</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>66</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>23330051920107</v>
+      </c>
+      <c r="B34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" t="s">
+        <v>161</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>23330051920108</v>
+      </c>
+      <c r="B35" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" t="s">
+        <v>162</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>66</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>23330051920110</v>
+      </c>
+      <c r="B36" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" t="s">
+        <v>163</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>23330051920111</v>
+      </c>
+      <c r="B37" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" t="s">
+        <v>164</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>66</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>23330051920114</v>
+      </c>
+      <c r="B38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" t="s">
+        <v>165</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
+        <v>66</v>
+      </c>
+      <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>23330051920115</v>
+      </c>
+      <c r="B39" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" t="s">
+        <v>132</v>
+      </c>
+      <c r="D39" t="s">
+        <v>166</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s">
+        <v>66</v>
+      </c>
+      <c r="G39">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ALCM - Estadisticos 20232.xlsx
+++ b/grupos/2ALCM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
   <si>
     <t>Materia</t>
   </si>
@@ -218,9 +218,6 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
     <t>Sanchez Morales Gilberto</t>
   </si>
   <si>
@@ -239,6 +236,9 @@
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -254,6 +254,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -266,82 +269,7 @@
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>ALTAMIRA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>AZPIRI</t>
-  </si>
-  <si>
-    <t>BONOLA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ESCOBEDO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
+    <t>BAEZ</t>
   </si>
   <si>
     <t>ANTONIO</t>
@@ -353,70 +281,7 @@
     <t>OLMOS</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VARILLAS</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>CARPINTEYRO</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MIXTECO</t>
+    <t>YAMILETH</t>
   </si>
   <si>
     <t>YAMILET</t>
@@ -429,96 +294,6 @@
   </si>
   <si>
     <t>MARGARITA</t>
-  </si>
-  <si>
-    <t>LINET</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>ANGEL NAIN</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>OSWALDO</t>
-  </si>
-  <si>
-    <t>JANETH</t>
-  </si>
-  <si>
-    <t>ILSE JIMENA</t>
-  </si>
-  <si>
-    <t>DAYANA ASTRID</t>
-  </si>
-  <si>
-    <t>MARIAM MICHAELL</t>
-  </si>
-  <si>
-    <t>LAURA ISABEL</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>ALEX TADEO</t>
-  </si>
-  <si>
-    <t>YEIMI ALEXANDER</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
-    <t>ANGEL EDUC</t>
-  </si>
-  <si>
-    <t>AXEL JOSUE</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>REY</t>
-  </si>
-  <si>
-    <t>ARELI DANAE</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ANIELA SAMANTA</t>
-  </si>
-  <si>
-    <t>CONCEPCION GUADALUPE</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>DAFNE</t>
-  </si>
-  <si>
-    <t>HEIDI</t>
-  </si>
-  <si>
-    <t>ARIADNA JARETZI</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>GUADALUPE ANAHI</t>
   </si>
 </sst>
 </file>
@@ -1158,7 +933,7 @@
         <v>7</v>
       </c>
       <c r="AJ4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK4">
         <v>8</v>
@@ -1271,7 +1046,7 @@
         <v>6</v>
       </c>
       <c r="AJ5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK5">
         <v>7</v>
@@ -1384,7 +1159,7 @@
         <v>6</v>
       </c>
       <c r="AJ6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK6">
         <v>6</v>
@@ -1497,7 +1272,7 @@
         <v>6</v>
       </c>
       <c r="AJ7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK7">
         <v>7</v>
@@ -1610,7 +1385,7 @@
         <v>6</v>
       </c>
       <c r="AJ8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK8">
         <v>6</v>
@@ -1723,7 +1498,7 @@
         <v>9</v>
       </c>
       <c r="AJ9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK9">
         <v>8</v>
@@ -1836,7 +1611,7 @@
         <v>6</v>
       </c>
       <c r="AJ10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK10">
         <v>8</v>
@@ -1949,7 +1724,7 @@
         <v>7</v>
       </c>
       <c r="AJ11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK11">
         <v>8</v>
@@ -2062,7 +1837,7 @@
         <v>6</v>
       </c>
       <c r="AJ12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK12">
         <v>8</v>
@@ -2175,7 +1950,7 @@
         <v>9</v>
       </c>
       <c r="AJ13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK13">
         <v>9</v>
@@ -2288,7 +2063,7 @@
         <v>6</v>
       </c>
       <c r="AJ14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK14">
         <v>7</v>
@@ -2401,7 +2176,7 @@
         <v>5</v>
       </c>
       <c r="AJ15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AK15">
         <v>5</v>
@@ -2514,7 +2289,7 @@
         <v>9</v>
       </c>
       <c r="AJ16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK16">
         <v>8</v>
@@ -2627,7 +2402,7 @@
         <v>5</v>
       </c>
       <c r="AJ17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AK17">
         <v>5</v>
@@ -2740,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="AJ18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK18">
         <v>7</v>
@@ -2853,7 +2628,7 @@
         <v>6</v>
       </c>
       <c r="AJ19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK19">
         <v>7</v>
@@ -2966,7 +2741,7 @@
         <v>6</v>
       </c>
       <c r="AJ20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK20">
         <v>7</v>
@@ -3079,7 +2854,7 @@
         <v>5</v>
       </c>
       <c r="AJ21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AK21">
         <v>5</v>
@@ -3192,7 +2967,7 @@
         <v>7</v>
       </c>
       <c r="AJ22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK22">
         <v>8</v>
@@ -3305,7 +3080,7 @@
         <v>5</v>
       </c>
       <c r="AJ23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK23">
         <v>6</v>
@@ -3418,7 +3193,7 @@
         <v>7</v>
       </c>
       <c r="AJ24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK24">
         <v>9</v>
@@ -3531,7 +3306,7 @@
         <v>8</v>
       </c>
       <c r="AJ25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK25">
         <v>7</v>
@@ -3644,7 +3419,7 @@
         <v>8</v>
       </c>
       <c r="AJ26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK26">
         <v>9</v>
@@ -3757,7 +3532,7 @@
         <v>5</v>
       </c>
       <c r="AJ27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK27">
         <v>6</v>
@@ -3870,7 +3645,7 @@
         <v>7</v>
       </c>
       <c r="AJ28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK28">
         <v>6</v>
@@ -3983,7 +3758,7 @@
         <v>7</v>
       </c>
       <c r="AJ29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK29">
         <v>8</v>
@@ -4096,7 +3871,7 @@
         <v>8</v>
       </c>
       <c r="AJ30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK30">
         <v>7</v>
@@ -4209,7 +3984,7 @@
         <v>9</v>
       </c>
       <c r="AJ31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK31">
         <v>8</v>
@@ -4322,7 +4097,7 @@
         <v>5</v>
       </c>
       <c r="AJ32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK32">
         <v>6</v>
@@ -4435,7 +4210,7 @@
         <v>6</v>
       </c>
       <c r="AJ33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK33">
         <v>8</v>
@@ -4548,7 +4323,7 @@
         <v>9</v>
       </c>
       <c r="AJ34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK34">
         <v>10</v>
@@ -4661,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="AJ35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK35">
         <v>7</v>
@@ -4774,7 +4549,7 @@
         <v>9</v>
       </c>
       <c r="AJ36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK36">
         <v>10</v>
@@ -4887,7 +4662,7 @@
         <v>7</v>
       </c>
       <c r="AJ37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK37">
         <v>6</v>
@@ -5000,7 +4775,7 @@
         <v>8</v>
       </c>
       <c r="AJ38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK38">
         <v>8</v>
@@ -5113,7 +4888,7 @@
         <v>6</v>
       </c>
       <c r="AJ39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK39">
         <v>6</v>
@@ -5226,7 +5001,7 @@
         <v>5</v>
       </c>
       <c r="AJ40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK40">
         <v>6</v>
@@ -5339,7 +5114,7 @@
         <v>8</v>
       </c>
       <c r="AJ41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK41">
         <v>7</v>
@@ -5452,7 +5227,7 @@
         <v>6</v>
       </c>
       <c r="AJ42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AK42">
         <v>8</v>
@@ -9012,7 +8787,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
@@ -9021,27 +8796,30 @@
         <v>39</v>
       </c>
       <c r="D2">
+        <v>31</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2">
+        <v>79.5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>39</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -9050,19 +8828,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>79.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>20.5</v>
+        <v>15.4</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -9073,7 +8851,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -9082,19 +8860,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>84.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="G4" s="2">
-        <v>15.4</v>
+        <v>10.3</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -9105,7 +8883,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
@@ -9114,19 +8892,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>89.7</v>
+        <v>92.3</v>
       </c>
       <c r="G5" s="2">
-        <v>10.3</v>
+        <v>7.7</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -9137,7 +8915,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
@@ -9158,7 +8936,7 @@
         <v>7.7</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -9169,7 +8947,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -9190,7 +8968,7 @@
         <v>7.7</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -9201,7 +8979,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>72</v>
@@ -9222,7 +9000,7 @@
         <v>7.7</v>
       </c>
       <c r="H8">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -9236,7 +9014,7 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9">
         <v>39</v>
@@ -9336,7 +9114,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9368,19 +9146,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920090</v>
+        <v>23330051920113</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>67</v>
@@ -9391,45 +9169,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920090</v>
+        <v>23330051920113</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>66</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920101</v>
+        <v>23330051920090</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -9440,22 +9218,22 @@
         <v>23330051920101</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>66</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -9463,19 +9241,19 @@
         <v>23330051920105</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -9483,761 +9261,25 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920105</v>
+        <v>23330051920112</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920112</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920112</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D9" t="s">
-        <v>136</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920078</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" t="s">
-        <v>137</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920077</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" t="s">
-        <v>138</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920079</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" t="s">
-        <v>139</v>
-      </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920080</v>
-      </c>
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" t="s">
-        <v>140</v>
-      </c>
-      <c r="E13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920082</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920081</v>
-      </c>
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" t="s">
-        <v>142</v>
-      </c>
-      <c r="E15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920085</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" t="s">
-        <v>143</v>
-      </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920086</v>
-      </c>
-      <c r="B17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" t="s">
-        <v>144</v>
-      </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920084</v>
-      </c>
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920087</v>
-      </c>
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" t="s">
-        <v>66</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920088</v>
-      </c>
-      <c r="B20" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" t="s">
-        <v>147</v>
-      </c>
-      <c r="E20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" t="s">
-        <v>66</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920089</v>
-      </c>
-      <c r="B21" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" t="s">
-        <v>148</v>
-      </c>
-      <c r="E21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920091</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" t="s">
-        <v>149</v>
-      </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920234</v>
-      </c>
-      <c r="B23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" t="s">
-        <v>150</v>
-      </c>
-      <c r="E23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920094</v>
-      </c>
-      <c r="B24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" t="s">
-        <v>122</v>
-      </c>
-      <c r="D24" t="s">
-        <v>151</v>
-      </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920251</v>
-      </c>
-      <c r="B25" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" t="s">
-        <v>152</v>
-      </c>
-      <c r="E25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" t="s">
-        <v>66</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>23330051920099</v>
-      </c>
-      <c r="B26" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" t="s">
-        <v>123</v>
-      </c>
-      <c r="D26" t="s">
-        <v>153</v>
-      </c>
-      <c r="E26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>23330051920098</v>
-      </c>
-      <c r="B27" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" t="s">
-        <v>124</v>
-      </c>
-      <c r="D27" t="s">
-        <v>154</v>
-      </c>
-      <c r="E27" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>23330051920100</v>
-      </c>
-      <c r="B28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" t="s">
-        <v>125</v>
-      </c>
-      <c r="D28" t="s">
-        <v>155</v>
-      </c>
-      <c r="E28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" t="s">
-        <v>66</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>23330051920102</v>
-      </c>
-      <c r="B29" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" t="s">
-        <v>156</v>
-      </c>
-      <c r="E29" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>23330051920103</v>
-      </c>
-      <c r="B30" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" t="s">
-        <v>99</v>
-      </c>
-      <c r="D30" t="s">
-        <v>157</v>
-      </c>
-      <c r="E30" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" t="s">
-        <v>66</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>23330051920104</v>
-      </c>
-      <c r="B31" t="s">
-        <v>100</v>
-      </c>
-      <c r="C31" t="s">
-        <v>127</v>
-      </c>
-      <c r="D31" t="s">
-        <v>158</v>
-      </c>
-      <c r="E31" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>23330051920261</v>
-      </c>
-      <c r="B32" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" t="s">
-        <v>128</v>
-      </c>
-      <c r="D32" t="s">
-        <v>159</v>
-      </c>
-      <c r="E32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" t="s">
-        <v>66</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>23330051920106</v>
-      </c>
-      <c r="B33" t="s">
-        <v>102</v>
-      </c>
-      <c r="C33" t="s">
-        <v>129</v>
-      </c>
-      <c r="D33" t="s">
-        <v>160</v>
-      </c>
-      <c r="E33" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" t="s">
-        <v>66</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>23330051920107</v>
-      </c>
-      <c r="B34" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" t="s">
-        <v>91</v>
-      </c>
-      <c r="D34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" t="s">
-        <v>66</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>23330051920108</v>
-      </c>
-      <c r="B35" t="s">
-        <v>104</v>
-      </c>
-      <c r="C35" t="s">
-        <v>130</v>
-      </c>
-      <c r="D35" t="s">
-        <v>162</v>
-      </c>
-      <c r="E35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" t="s">
-        <v>66</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>23330051920110</v>
-      </c>
-      <c r="B36" t="s">
-        <v>105</v>
-      </c>
-      <c r="C36" t="s">
-        <v>131</v>
-      </c>
-      <c r="D36" t="s">
-        <v>163</v>
-      </c>
-      <c r="E36" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>23330051920111</v>
-      </c>
-      <c r="B37" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" t="s">
-        <v>164</v>
-      </c>
-      <c r="E37" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>23330051920114</v>
-      </c>
-      <c r="B38" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" t="s">
-        <v>99</v>
-      </c>
-      <c r="D38" t="s">
-        <v>165</v>
-      </c>
-      <c r="E38" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" t="s">
-        <v>66</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>23330051920115</v>
-      </c>
-      <c r="B39" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" t="s">
-        <v>132</v>
-      </c>
-      <c r="D39" t="s">
-        <v>166</v>
-      </c>
-      <c r="E39" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" t="s">
-        <v>66</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
